--- a/artfynd/A 35413-2025 artfynd.xlsx
+++ b/artfynd/A 35413-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127460599</v>
       </c>
       <c r="B2" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>127460595</v>
       </c>
       <c r="B3" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>127460615</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>127460587</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>127460642</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35413-2025 artfynd.xlsx
+++ b/artfynd/A 35413-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127460599</v>
       </c>
       <c r="B2" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>127460595</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>127460587</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>127460642</v>
       </c>
       <c r="B6" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35413-2025 artfynd.xlsx
+++ b/artfynd/A 35413-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127460599</v>
+        <v>127460595</v>
       </c>
       <c r="B2" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543610</v>
+        <v>543624</v>
       </c>
       <c r="R2" t="n">
-        <v>6686046</v>
+        <v>6686039</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127460595</v>
+        <v>127460599</v>
       </c>
       <c r="B3" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543624</v>
+        <v>543610</v>
       </c>
       <c r="R3" t="n">
-        <v>6686039</v>
+        <v>6686046</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -918,7 +918,7 @@
         <v>127460615</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>127460587</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>127460642</v>
       </c>
       <c r="B6" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35413-2025 artfynd.xlsx
+++ b/artfynd/A 35413-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127460595</v>
+        <v>127460599</v>
       </c>
       <c r="B2" t="n">
         <v>98450</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543624</v>
+        <v>543610</v>
       </c>
       <c r="R2" t="n">
-        <v>6686039</v>
+        <v>6686046</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -795,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127460599</v>
+        <v>127460595</v>
       </c>
       <c r="B3" t="n">
         <v>98450</v>
@@ -825,7 +825,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543610</v>
+        <v>543624</v>
       </c>
       <c r="R3" t="n">
-        <v>6686046</v>
+        <v>6686039</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 35413-2025 artfynd.xlsx
+++ b/artfynd/A 35413-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1272,6 +1272,2103 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127773860</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91332</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Linsjön, Linsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>543492</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6685995</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127777665</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>543699</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6686040</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127777982</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91332</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Linsjön, Linsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>543573</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6686069</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127777767</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Linsjön, Linsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>543646</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6686005</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127773929</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91786</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Linsjön, Linsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>543504</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6685984</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127778397</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91332</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Linsjön, Linsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>543496</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6686038</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127773942</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91332</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Linsjön, Linsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>543500</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6685988</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127774230</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91786</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lertjärnen, Lertjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>543512</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6685999</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127774327</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91786</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Linsjön, Linsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>543519</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6686003</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127777519</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91297</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>543706</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6685997</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127774283</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91332</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Linsjön, Linsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>543516</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6686000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127780329</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91332</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lertjärnen, Lertjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>543485</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6685997</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127777861</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91332</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Linsjön, Linsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>543554</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6686028</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127778276</v>
+      </c>
+      <c r="B20" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Linsjön, Linsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>543535</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6686018</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127778321</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91332</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Linsjön, Linsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>543535</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6686018</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127777566</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91332</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>543701</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6686004</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127777450</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91297</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Linsjön, Linsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>543685</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6685977</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127776605</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lertjärnen, Lertjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>543597</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6685995</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127776541</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lertjärnen, Lertjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>543597</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6685994</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Tätt med plantor på ca 2 m2. Cirka 20 överblommade blomställningarna.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127773913</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91332</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Linsjön, Linsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>543494</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6685991</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127777553</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91332</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>543709</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6686001</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35413-2025 artfynd.xlsx
+++ b/artfynd/A 35413-2025 artfynd.xlsx
@@ -1371,45 +1371,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127777665</v>
+        <v>127777982</v>
       </c>
       <c r="B8" t="n">
-        <v>98450</v>
+        <v>91332</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
+          <t>Linsjön, Linsjön, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543699</v>
+        <v>543573</v>
       </c>
       <c r="R8" t="n">
-        <v>6686040</v>
+        <v>6686069</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1468,45 +1468,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127777982</v>
+        <v>127777665</v>
       </c>
       <c r="B9" t="n">
-        <v>91332</v>
+        <v>98450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Linsjön, Linsjön, Dlr</t>
+          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543573</v>
+        <v>543699</v>
       </c>
       <c r="R9" t="n">
-        <v>6686069</v>
+        <v>6686040</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1565,32 +1565,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127777767</v>
+        <v>127778397</v>
       </c>
       <c r="B10" t="n">
-        <v>98450</v>
+        <v>91332</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543646</v>
+        <v>543496</v>
       </c>
       <c r="R10" t="n">
-        <v>6686005</v>
+        <v>6686038</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1759,32 +1759,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127778397</v>
+        <v>127777767</v>
       </c>
       <c r="B12" t="n">
-        <v>91332</v>
+        <v>98450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543496</v>
+        <v>543646</v>
       </c>
       <c r="R12" t="n">
-        <v>6686038</v>
+        <v>6686005</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2157,45 +2157,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127777519</v>
+        <v>127774283</v>
       </c>
       <c r="B16" t="n">
-        <v>91297</v>
+        <v>91332</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
+          <t>Linsjön, Linsjön, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543706</v>
+        <v>543516</v>
       </c>
       <c r="R16" t="n">
-        <v>6685997</v>
+        <v>6686000</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2254,7 +2254,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127774283</v>
+        <v>127780329</v>
       </c>
       <c r="B17" t="n">
         <v>91332</v>
@@ -2285,17 +2285,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Linsjön, Linsjön, Dlr</t>
+          <t>Lertjärnen, Lertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>543516</v>
+        <v>543485</v>
       </c>
       <c r="R17" t="n">
-        <v>6686000</v>
+        <v>6685997</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2322,9 +2322,19 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2339,60 +2349,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127780329</v>
+        <v>127777519</v>
       </c>
       <c r="B18" t="n">
-        <v>91332</v>
+        <v>91297</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lertjärnen, Lertjärnen, Dlr</t>
+          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543485</v>
+        <v>543706</v>
       </c>
       <c r="R18" t="n">
         <v>6685997</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2419,19 +2429,9 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>16:29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2446,12 +2446,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3053,60 +3053,55 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+          <t>Cecilia Rastad, Åke Persson, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127776541</v>
+        <v>127773913</v>
       </c>
       <c r="B25" t="n">
-        <v>98450</v>
+        <v>91332</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lertjärnen, Lertjärnen, Dlr</t>
+          <t>Linsjön, Linsjön, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>543597</v>
+        <v>543494</v>
       </c>
       <c r="R25" t="n">
-        <v>6685994</v>
+        <v>6685991</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3133,24 +3128,9 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Tätt med plantor på ca 2 m2. Cirka 20 överblommade blomställningarna.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3165,60 +3145,65 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127773913</v>
+        <v>127776541</v>
       </c>
       <c r="B26" t="n">
-        <v>91332</v>
+        <v>98450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Linsjön, Linsjön, Dlr</t>
+          <t>Lertjärnen, Lertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>543494</v>
+        <v>543597</v>
       </c>
       <c r="R26" t="n">
-        <v>6685991</v>
+        <v>6685994</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3245,9 +3230,24 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Tätt med plantor på ca 2 m2. Cirka 20 överblommade blomställningarna.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3262,12 +3262,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Cecilia Rastad, Åke Persson, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 35413-2025 artfynd.xlsx
+++ b/artfynd/A 35413-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127460599</v>
+        <v>127460595</v>
       </c>
       <c r="B2" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543610</v>
+        <v>543624</v>
       </c>
       <c r="R2" t="n">
-        <v>6686046</v>
+        <v>6686039</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127460595</v>
+        <v>127460599</v>
       </c>
       <c r="B3" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543624</v>
+        <v>543610</v>
       </c>
       <c r="R3" t="n">
-        <v>6686039</v>
+        <v>6686046</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1037,7 +1037,7 @@
         <v>127460587</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>127460642</v>
       </c>
       <c r="B6" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>127773860</v>
       </c>
       <c r="B7" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,45 +1371,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127777982</v>
+        <v>127777665</v>
       </c>
       <c r="B8" t="n">
-        <v>91332</v>
+        <v>98456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Linsjön, Linsjön, Dlr</t>
+          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543573</v>
+        <v>543699</v>
       </c>
       <c r="R8" t="n">
-        <v>6686069</v>
+        <v>6686040</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1468,45 +1468,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127777665</v>
+        <v>127777982</v>
       </c>
       <c r="B9" t="n">
-        <v>98450</v>
+        <v>91338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
+          <t>Linsjön, Linsjön, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543699</v>
+        <v>543573</v>
       </c>
       <c r="R9" t="n">
-        <v>6686040</v>
+        <v>6686069</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1565,32 +1565,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127778397</v>
+        <v>127773929</v>
       </c>
       <c r="B10" t="n">
-        <v>91332</v>
+        <v>91792</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543496</v>
+        <v>543504</v>
       </c>
       <c r="R10" t="n">
-        <v>6686038</v>
+        <v>6685984</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1662,32 +1662,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127773929</v>
+        <v>127778397</v>
       </c>
       <c r="B11" t="n">
-        <v>91786</v>
+        <v>91338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543504</v>
+        <v>543496</v>
       </c>
       <c r="R11" t="n">
-        <v>6685984</v>
+        <v>6686038</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1762,7 +1762,7 @@
         <v>127777767</v>
       </c>
       <c r="B12" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>127773942</v>
       </c>
       <c r="B13" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,10 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127774230</v>
+        <v>127774327</v>
       </c>
       <c r="B14" t="n">
-        <v>91786</v>
+        <v>91792</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1984,17 +1984,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lertjärnen, Lertjärnen, Dlr</t>
+          <t>Linsjön, Linsjön, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543512</v>
+        <v>543519</v>
       </c>
       <c r="R14" t="n">
-        <v>6685999</v>
+        <v>6686003</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2021,19 +2021,9 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2048,44 +2038,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127774327</v>
+        <v>127774283</v>
       </c>
       <c r="B15" t="n">
-        <v>91786</v>
+        <v>91338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2095,10 +2085,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543519</v>
+        <v>543516</v>
       </c>
       <c r="R15" t="n">
-        <v>6686003</v>
+        <v>6686000</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2157,45 +2147,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127774283</v>
+        <v>127777519</v>
       </c>
       <c r="B16" t="n">
-        <v>91332</v>
+        <v>91303</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Linsjön, Linsjön, Dlr</t>
+          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543516</v>
+        <v>543706</v>
       </c>
       <c r="R16" t="n">
-        <v>6686000</v>
+        <v>6685997</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2254,10 +2244,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127780329</v>
+        <v>127777861</v>
       </c>
       <c r="B17" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2285,17 +2275,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lertjärnen, Lertjärnen, Dlr</t>
+          <t>Linsjön, Linsjön, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>543485</v>
+        <v>543554</v>
       </c>
       <c r="R17" t="n">
-        <v>6685997</v>
+        <v>6686028</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2322,19 +2312,9 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>16:29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2349,22 +2329,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127777519</v>
+        <v>127778276</v>
       </c>
       <c r="B18" t="n">
-        <v>91297</v>
+        <v>5177</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2372,34 +2352,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
+          <t>Linsjön, Linsjön, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543706</v>
+        <v>543535</v>
       </c>
       <c r="R18" t="n">
-        <v>6685997</v>
+        <v>6686018</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2440,6 +2429,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2458,10 +2448,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127777861</v>
+        <v>127778321</v>
       </c>
       <c r="B19" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2493,10 +2483,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>543554</v>
+        <v>543535</v>
       </c>
       <c r="R19" t="n">
-        <v>6686028</v>
+        <v>6686018</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2555,54 +2545,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127778276</v>
+        <v>127777566</v>
       </c>
       <c r="B20" t="n">
-        <v>5177</v>
+        <v>91338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Linsjön, Linsjön, Dlr</t>
+          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>543535</v>
+        <v>543701</v>
       </c>
       <c r="R20" t="n">
-        <v>6686018</v>
+        <v>6686004</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2643,7 +2624,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2662,32 +2642,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127778321</v>
+        <v>127777450</v>
       </c>
       <c r="B21" t="n">
-        <v>91332</v>
+        <v>91303</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2697,10 +2677,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>543535</v>
+        <v>543685</v>
       </c>
       <c r="R21" t="n">
-        <v>6686018</v>
+        <v>6685977</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2759,10 +2739,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127777566</v>
+        <v>127773913</v>
       </c>
       <c r="B22" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2790,14 +2770,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
+          <t>Linsjön, Linsjön, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>543701</v>
+        <v>543494</v>
       </c>
       <c r="R22" t="n">
-        <v>6686004</v>
+        <v>6685991</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2856,45 +2836,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127777450</v>
+        <v>127777553</v>
       </c>
       <c r="B23" t="n">
-        <v>91297</v>
+        <v>91338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Linsjön, Linsjön, Dlr</t>
+          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>543685</v>
+        <v>543709</v>
       </c>
       <c r="R23" t="n">
-        <v>6685977</v>
+        <v>6686001</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2953,10 +2933,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127776605</v>
+        <v>127774230</v>
       </c>
       <c r="B24" t="n">
-        <v>98450</v>
+        <v>91792</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2964,37 +2944,40 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lertjärnen, Lertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>543597</v>
+        <v>543512</v>
       </c>
       <c r="R24" t="n">
-        <v>6685995</v>
+        <v>6685999</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3023,7 +3006,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3033,7 +3016,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3042,6 +3025,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3053,17 +3037,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åke Persson, Stig-Åke Svenson</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127773913</v>
+        <v>127780329</v>
       </c>
       <c r="B25" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3089,19 +3073,22 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Linsjön, Linsjön, Dlr</t>
+          <t>Lertjärnen, Lertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>543494</v>
+        <v>543485</v>
       </c>
       <c r="R25" t="n">
-        <v>6685991</v>
+        <v>6685997</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3128,39 +3115,50 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127776541</v>
+        <v>127776605</v>
       </c>
       <c r="B26" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3186,11 +3184,6 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lertjärnen, Lertjärnen, Dlr</t>
@@ -3200,7 +3193,7 @@
         <v>543597</v>
       </c>
       <c r="R26" t="n">
-        <v>6685994</v>
+        <v>6685995</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3232,7 +3225,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3242,12 +3235,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Tätt med plantor på ca 2 m2. Cirka 20 överblommade blomställningarna.</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3267,55 +3255,60 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åke Persson, Stig-Åke Svenson</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127777553</v>
+        <v>127776541</v>
       </c>
       <c r="B27" t="n">
-        <v>91332</v>
+        <v>98456</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
+          <t>Lertjärnen, Lertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>543709</v>
+        <v>543597</v>
       </c>
       <c r="R27" t="n">
-        <v>6686001</v>
+        <v>6685994</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3342,9 +3335,24 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Tätt med plantor på ca 2 m2. Cirka 20 överblommade blomställningarna.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3359,12 +3367,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 35413-2025 artfynd.xlsx
+++ b/artfynd/A 35413-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127460595</v>
+        <v>127460599</v>
       </c>
       <c r="B2" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543624</v>
+        <v>543610</v>
       </c>
       <c r="R2" t="n">
-        <v>6686039</v>
+        <v>6686046</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127460599</v>
+        <v>127460595</v>
       </c>
       <c r="B3" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543610</v>
+        <v>543624</v>
       </c>
       <c r="R3" t="n">
-        <v>6686046</v>
+        <v>6686039</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -918,7 +918,7 @@
         <v>127460615</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>127460587</v>
       </c>
       <c r="B5" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>127460642</v>
       </c>
       <c r="B6" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>127773860</v>
       </c>
       <c r="B7" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,45 +1371,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127777665</v>
+        <v>127777982</v>
       </c>
       <c r="B8" t="n">
-        <v>98456</v>
+        <v>91341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
+          <t>Linsjön, Linsjön, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543699</v>
+        <v>543573</v>
       </c>
       <c r="R8" t="n">
-        <v>6686040</v>
+        <v>6686069</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1468,45 +1468,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127777982</v>
+        <v>127777665</v>
       </c>
       <c r="B9" t="n">
-        <v>91338</v>
+        <v>98459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Linsjön, Linsjön, Dlr</t>
+          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543573</v>
+        <v>543699</v>
       </c>
       <c r="R9" t="n">
-        <v>6686069</v>
+        <v>6686040</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1565,32 +1565,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127773929</v>
+        <v>127778397</v>
       </c>
       <c r="B10" t="n">
-        <v>91792</v>
+        <v>91341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543504</v>
+        <v>543496</v>
       </c>
       <c r="R10" t="n">
-        <v>6685984</v>
+        <v>6686038</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1662,32 +1662,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127778397</v>
+        <v>127773929</v>
       </c>
       <c r="B11" t="n">
-        <v>91338</v>
+        <v>91795</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543496</v>
+        <v>543504</v>
       </c>
       <c r="R11" t="n">
-        <v>6686038</v>
+        <v>6685984</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1762,7 +1762,7 @@
         <v>127777767</v>
       </c>
       <c r="B12" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>127773942</v>
       </c>
       <c r="B13" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>127774327</v>
       </c>
       <c r="B14" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>127774283</v>
       </c>
       <c r="B15" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>127777519</v>
       </c>
       <c r="B16" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>127777861</v>
       </c>
       <c r="B17" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>127778321</v>
       </c>
       <c r="B19" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>127777566</v>
       </c>
       <c r="B20" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>127777450</v>
       </c>
       <c r="B21" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>127773913</v>
       </c>
       <c r="B22" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>127777553</v>
       </c>
       <c r="B23" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>127774230</v>
       </c>
       <c r="B24" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>127780329</v>
       </c>
       <c r="B25" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>127776605</v>
       </c>
       <c r="B26" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>127776541</v>
       </c>
       <c r="B27" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 35413-2025 artfynd.xlsx
+++ b/artfynd/A 35413-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127460599</v>
       </c>
       <c r="B2" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>127460595</v>
       </c>
       <c r="B3" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>127460615</v>
       </c>
       <c r="B4" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>127460587</v>
       </c>
       <c r="B5" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>127460642</v>
       </c>
       <c r="B6" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>127773860</v>
       </c>
       <c r="B7" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,45 +1371,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127777982</v>
+        <v>127777665</v>
       </c>
       <c r="B8" t="n">
-        <v>91341</v>
+        <v>98467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Linsjön, Linsjön, Dlr</t>
+          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543573</v>
+        <v>543699</v>
       </c>
       <c r="R8" t="n">
-        <v>6686069</v>
+        <v>6686040</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1468,45 +1468,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127777665</v>
+        <v>127777982</v>
       </c>
       <c r="B9" t="n">
-        <v>98459</v>
+        <v>91349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
+          <t>Linsjön, Linsjön, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543699</v>
+        <v>543573</v>
       </c>
       <c r="R9" t="n">
-        <v>6686040</v>
+        <v>6686069</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1565,32 +1565,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127778397</v>
+        <v>127773929</v>
       </c>
       <c r="B10" t="n">
-        <v>91341</v>
+        <v>91803</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543496</v>
+        <v>543504</v>
       </c>
       <c r="R10" t="n">
-        <v>6686038</v>
+        <v>6685984</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1662,32 +1662,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127773929</v>
+        <v>127778397</v>
       </c>
       <c r="B11" t="n">
-        <v>91795</v>
+        <v>91349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543504</v>
+        <v>543496</v>
       </c>
       <c r="R11" t="n">
-        <v>6685984</v>
+        <v>6686038</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1762,7 +1762,7 @@
         <v>127777767</v>
       </c>
       <c r="B12" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>127773942</v>
       </c>
       <c r="B13" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>127774327</v>
       </c>
       <c r="B14" t="n">
-        <v>91795</v>
+        <v>91803</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>127774283</v>
       </c>
       <c r="B15" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>127777519</v>
       </c>
       <c r="B16" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>127777861</v>
       </c>
       <c r="B17" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>127778321</v>
       </c>
       <c r="B19" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>127777566</v>
       </c>
       <c r="B20" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>127777450</v>
       </c>
       <c r="B21" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>127773913</v>
       </c>
       <c r="B22" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>127777553</v>
       </c>
       <c r="B23" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>127774230</v>
       </c>
       <c r="B24" t="n">
-        <v>91795</v>
+        <v>91803</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>127780329</v>
       </c>
       <c r="B25" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>127776605</v>
       </c>
       <c r="B26" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>127776541</v>
       </c>
       <c r="B27" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 35413-2025 artfynd.xlsx
+++ b/artfynd/A 35413-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127460599</v>
       </c>
       <c r="B2" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>127460595</v>
       </c>
       <c r="B3" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>127460587</v>
       </c>
       <c r="B5" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>127460642</v>
       </c>
       <c r="B6" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>127773860</v>
       </c>
       <c r="B7" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,45 +1371,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127777665</v>
+        <v>127777982</v>
       </c>
       <c r="B8" t="n">
-        <v>98467</v>
+        <v>91350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
+          <t>Linsjön, Linsjön, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543699</v>
+        <v>543573</v>
       </c>
       <c r="R8" t="n">
-        <v>6686040</v>
+        <v>6686069</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1468,45 +1468,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127777982</v>
+        <v>127777665</v>
       </c>
       <c r="B9" t="n">
-        <v>91349</v>
+        <v>98468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Linsjön, Linsjön, Dlr</t>
+          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543573</v>
+        <v>543699</v>
       </c>
       <c r="R9" t="n">
-        <v>6686069</v>
+        <v>6686040</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1568,7 +1568,7 @@
         <v>127773929</v>
       </c>
       <c r="B10" t="n">
-        <v>91803</v>
+        <v>91804</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>127778397</v>
       </c>
       <c r="B11" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>127777767</v>
       </c>
       <c r="B12" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>127773942</v>
       </c>
       <c r="B13" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>127774327</v>
       </c>
       <c r="B14" t="n">
-        <v>91803</v>
+        <v>91804</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>127774283</v>
       </c>
       <c r="B15" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>127777519</v>
       </c>
       <c r="B16" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>127777861</v>
       </c>
       <c r="B17" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>127778321</v>
       </c>
       <c r="B19" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>127777566</v>
       </c>
       <c r="B20" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>127777450</v>
       </c>
       <c r="B21" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>127773913</v>
       </c>
       <c r="B22" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>127777553</v>
       </c>
       <c r="B23" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>127774230</v>
       </c>
       <c r="B24" t="n">
-        <v>91803</v>
+        <v>91804</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson, Patric Engfeldt</t>
+          <t>Cecilia Rastad, Åke Persson, Stig-Åke Svenson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3047,7 +3047,7 @@
         <v>127780329</v>
       </c>
       <c r="B25" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>127776605</v>
       </c>
       <c r="B26" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>127776541</v>
       </c>
       <c r="B27" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 35413-2025 artfynd.xlsx
+++ b/artfynd/A 35413-2025 artfynd.xlsx
@@ -3037,7 +3037,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åke Persson, Stig-Åke Svenson, Patric Engfeldt</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 35413-2025 artfynd.xlsx
+++ b/artfynd/A 35413-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127460599</v>
+        <v>127460595</v>
       </c>
       <c r="B2" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543610</v>
+        <v>543624</v>
       </c>
       <c r="R2" t="n">
-        <v>6686046</v>
+        <v>6686039</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127460595</v>
+        <v>127460599</v>
       </c>
       <c r="B3" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543624</v>
+        <v>543610</v>
       </c>
       <c r="R3" t="n">
-        <v>6686039</v>
+        <v>6686046</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1037,7 +1037,7 @@
         <v>127460587</v>
       </c>
       <c r="B5" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>127460642</v>
       </c>
       <c r="B6" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>127773860</v>
       </c>
       <c r="B7" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>127777982</v>
       </c>
       <c r="B8" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>127777665</v>
       </c>
       <c r="B9" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1565,32 +1565,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127773929</v>
+        <v>127778397</v>
       </c>
       <c r="B10" t="n">
-        <v>91804</v>
+        <v>91351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543504</v>
+        <v>543496</v>
       </c>
       <c r="R10" t="n">
-        <v>6685984</v>
+        <v>6686038</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1662,32 +1662,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127778397</v>
+        <v>127773929</v>
       </c>
       <c r="B11" t="n">
-        <v>91350</v>
+        <v>91805</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543496</v>
+        <v>543504</v>
       </c>
       <c r="R11" t="n">
-        <v>6686038</v>
+        <v>6685984</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1762,7 +1762,7 @@
         <v>127777767</v>
       </c>
       <c r="B12" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>127773942</v>
       </c>
       <c r="B13" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>127774327</v>
       </c>
       <c r="B14" t="n">
-        <v>91804</v>
+        <v>91805</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2050,45 +2050,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127774283</v>
+        <v>127777519</v>
       </c>
       <c r="B15" t="n">
-        <v>91350</v>
+        <v>91316</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Linsjön, Linsjön, Dlr</t>
+          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543516</v>
+        <v>543706</v>
       </c>
       <c r="R15" t="n">
-        <v>6686000</v>
+        <v>6685997</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2147,45 +2147,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127777519</v>
+        <v>127774283</v>
       </c>
       <c r="B16" t="n">
-        <v>91315</v>
+        <v>91351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
+          <t>Linsjön, Linsjön, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543706</v>
+        <v>543516</v>
       </c>
       <c r="R16" t="n">
-        <v>6685997</v>
+        <v>6686000</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2247,7 +2247,7 @@
         <v>127777861</v>
       </c>
       <c r="B17" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>127778321</v>
       </c>
       <c r="B19" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>127777566</v>
       </c>
       <c r="B20" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>127777450</v>
       </c>
       <c r="B21" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>127773913</v>
       </c>
       <c r="B22" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>127777553</v>
       </c>
       <c r="B23" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>127774230</v>
       </c>
       <c r="B24" t="n">
-        <v>91804</v>
+        <v>91805</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>127780329</v>
       </c>
       <c r="B25" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>127776605</v>
       </c>
       <c r="B26" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>127776541</v>
       </c>
       <c r="B27" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 35413-2025 artfynd.xlsx
+++ b/artfynd/A 35413-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127460595</v>
+        <v>127460599</v>
       </c>
       <c r="B2" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543624</v>
+        <v>543610</v>
       </c>
       <c r="R2" t="n">
-        <v>6686039</v>
+        <v>6686046</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127460599</v>
+        <v>127460595</v>
       </c>
       <c r="B3" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543610</v>
+        <v>543624</v>
       </c>
       <c r="R3" t="n">
-        <v>6686046</v>
+        <v>6686039</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1037,7 +1037,7 @@
         <v>127460587</v>
       </c>
       <c r="B5" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>127460642</v>
       </c>
       <c r="B6" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>127773860</v>
       </c>
       <c r="B7" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>127777982</v>
       </c>
       <c r="B8" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>127777665</v>
       </c>
       <c r="B9" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1565,32 +1565,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127778397</v>
+        <v>127777767</v>
       </c>
       <c r="B10" t="n">
-        <v>91351</v>
+        <v>98470</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543496</v>
+        <v>543646</v>
       </c>
       <c r="R10" t="n">
-        <v>6686038</v>
+        <v>6686005</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1665,7 +1665,7 @@
         <v>127773929</v>
       </c>
       <c r="B11" t="n">
-        <v>91805</v>
+        <v>91806</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1759,32 +1759,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127777767</v>
+        <v>127778397</v>
       </c>
       <c r="B12" t="n">
-        <v>98469</v>
+        <v>91352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543646</v>
+        <v>543496</v>
       </c>
       <c r="R12" t="n">
-        <v>6686005</v>
+        <v>6686038</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1859,7 +1859,7 @@
         <v>127773942</v>
       </c>
       <c r="B13" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>127774327</v>
       </c>
       <c r="B14" t="n">
-        <v>91805</v>
+        <v>91806</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2050,45 +2050,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127777519</v>
+        <v>127774283</v>
       </c>
       <c r="B15" t="n">
-        <v>91316</v>
+        <v>91352</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
+          <t>Linsjön, Linsjön, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543706</v>
+        <v>543516</v>
       </c>
       <c r="R15" t="n">
-        <v>6685997</v>
+        <v>6686000</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2147,45 +2147,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127774283</v>
+        <v>127777519</v>
       </c>
       <c r="B16" t="n">
-        <v>91351</v>
+        <v>91317</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Linsjön, Linsjön, Dlr</t>
+          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543516</v>
+        <v>543706</v>
       </c>
       <c r="R16" t="n">
-        <v>6686000</v>
+        <v>6685997</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2247,7 +2247,7 @@
         <v>127777861</v>
       </c>
       <c r="B17" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>127778321</v>
       </c>
       <c r="B19" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>127777566</v>
       </c>
       <c r="B20" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>127777450</v>
       </c>
       <c r="B21" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>127773913</v>
       </c>
       <c r="B22" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>127777553</v>
       </c>
       <c r="B23" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>127774230</v>
       </c>
       <c r="B24" t="n">
-        <v>91805</v>
+        <v>91806</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>127780329</v>
       </c>
       <c r="B25" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>127776605</v>
       </c>
       <c r="B26" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>127776541</v>
       </c>
       <c r="B27" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 35413-2025 artfynd.xlsx
+++ b/artfynd/A 35413-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127460599</v>
+        <v>127460595</v>
       </c>
       <c r="B2" t="n">
         <v>98470</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543610</v>
+        <v>543624</v>
       </c>
       <c r="R2" t="n">
-        <v>6686046</v>
+        <v>6686039</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -795,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127460595</v>
+        <v>127460599</v>
       </c>
       <c r="B3" t="n">
         <v>98470</v>
@@ -825,7 +825,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543624</v>
+        <v>543610</v>
       </c>
       <c r="R3" t="n">
-        <v>6686039</v>
+        <v>6686046</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1565,10 +1565,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127777767</v>
+        <v>127773929</v>
       </c>
       <c r="B10" t="n">
-        <v>98470</v>
+        <v>91806</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,21 +1576,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543646</v>
+        <v>543504</v>
       </c>
       <c r="R10" t="n">
-        <v>6686005</v>
+        <v>6685984</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1662,32 +1662,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127773929</v>
+        <v>127778397</v>
       </c>
       <c r="B11" t="n">
-        <v>91806</v>
+        <v>91352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543504</v>
+        <v>543496</v>
       </c>
       <c r="R11" t="n">
-        <v>6685984</v>
+        <v>6686038</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1759,32 +1759,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127778397</v>
+        <v>127777767</v>
       </c>
       <c r="B12" t="n">
-        <v>91352</v>
+        <v>98470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543496</v>
+        <v>543646</v>
       </c>
       <c r="R12" t="n">
-        <v>6686038</v>
+        <v>6686005</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2050,45 +2050,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127774283</v>
+        <v>127777519</v>
       </c>
       <c r="B15" t="n">
-        <v>91352</v>
+        <v>91317</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Linsjön, Linsjön, Dlr</t>
+          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543516</v>
+        <v>543706</v>
       </c>
       <c r="R15" t="n">
-        <v>6686000</v>
+        <v>6685997</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2147,45 +2147,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127777519</v>
+        <v>127774283</v>
       </c>
       <c r="B16" t="n">
-        <v>91317</v>
+        <v>91352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
+          <t>Linsjön, Linsjön, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543706</v>
+        <v>543516</v>
       </c>
       <c r="R16" t="n">
-        <v>6685997</v>
+        <v>6686000</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>

--- a/artfynd/A 35413-2025 artfynd.xlsx
+++ b/artfynd/A 35413-2025 artfynd.xlsx
@@ -2050,45 +2050,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127777519</v>
+        <v>127774283</v>
       </c>
       <c r="B15" t="n">
-        <v>91317</v>
+        <v>91352</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
+          <t>Linsjön, Linsjön, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543706</v>
+        <v>543516</v>
       </c>
       <c r="R15" t="n">
-        <v>6685997</v>
+        <v>6686000</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2147,45 +2147,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127774283</v>
+        <v>127777519</v>
       </c>
       <c r="B16" t="n">
-        <v>91352</v>
+        <v>91317</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Linsjön, Linsjön, Dlr</t>
+          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543516</v>
+        <v>543706</v>
       </c>
       <c r="R16" t="n">
-        <v>6686000</v>
+        <v>6685997</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>

--- a/artfynd/A 35413-2025 artfynd.xlsx
+++ b/artfynd/A 35413-2025 artfynd.xlsx
@@ -2050,45 +2050,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127774283</v>
+        <v>127777519</v>
       </c>
       <c r="B15" t="n">
-        <v>91352</v>
+        <v>91317</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Linsjön, Linsjön, Dlr</t>
+          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543516</v>
+        <v>543706</v>
       </c>
       <c r="R15" t="n">
-        <v>6686000</v>
+        <v>6685997</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2147,45 +2147,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127777519</v>
+        <v>127774283</v>
       </c>
       <c r="B16" t="n">
-        <v>91317</v>
+        <v>91352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
+          <t>Linsjön, Linsjön, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543706</v>
+        <v>543516</v>
       </c>
       <c r="R16" t="n">
-        <v>6685997</v>
+        <v>6686000</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>

--- a/artfynd/A 35413-2025 artfynd.xlsx
+++ b/artfynd/A 35413-2025 artfynd.xlsx
@@ -1277,7 +1277,7 @@
         <v>127773860</v>
       </c>
       <c r="B7" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>127777982</v>
       </c>
       <c r="B8" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>127777665</v>
       </c>
       <c r="B9" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>127773929</v>
       </c>
       <c r="B10" t="n">
-        <v>91806</v>
+        <v>91814</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>127778397</v>
       </c>
       <c r="B11" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>127777767</v>
       </c>
       <c r="B12" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>127773942</v>
       </c>
       <c r="B13" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>127774327</v>
       </c>
       <c r="B14" t="n">
-        <v>91806</v>
+        <v>91814</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2050,45 +2050,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127777519</v>
+        <v>127774283</v>
       </c>
       <c r="B15" t="n">
-        <v>91317</v>
+        <v>91360</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
+          <t>Linsjön, Linsjön, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543706</v>
+        <v>543516</v>
       </c>
       <c r="R15" t="n">
-        <v>6685997</v>
+        <v>6686000</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2147,45 +2147,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127774283</v>
+        <v>127777519</v>
       </c>
       <c r="B16" t="n">
-        <v>91352</v>
+        <v>91325</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Linsjön, Linsjön, Dlr</t>
+          <t>Vikmanshyttan, Vikmanshyttan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543516</v>
+        <v>543706</v>
       </c>
       <c r="R16" t="n">
-        <v>6686000</v>
+        <v>6685997</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2247,7 +2247,7 @@
         <v>127777861</v>
       </c>
       <c r="B17" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>127778321</v>
       </c>
       <c r="B19" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>127777566</v>
       </c>
       <c r="B20" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>127777450</v>
       </c>
       <c r="B21" t="n">
-        <v>91317</v>
+        <v>91325</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>127773913</v>
       </c>
       <c r="B22" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>127777553</v>
       </c>
       <c r="B23" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>127774230</v>
       </c>
       <c r="B24" t="n">
-        <v>91806</v>
+        <v>91814</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>127780329</v>
       </c>
       <c r="B25" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>127776605</v>
       </c>
       <c r="B26" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>127776541</v>
       </c>
       <c r="B27" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
